--- a/extenbooks/S515.xlsx
+++ b/extenbooks/S515.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=thousands</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=thousands</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES, units=thousands</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S515-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S515-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S515-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>29937</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>29937</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>30013</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>30013</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>30280</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>30280</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>31365</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>31365</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>32566</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>32566</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>32856</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>32856</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>33445</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>33445</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>34125</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>34125</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>33247</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>33247</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>32727</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>32727</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>33896</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>33896</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>35462</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>35462</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>35657</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>35657</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -588,6 +688,894 @@
       </c>
       <c r="B16" s="3" t="n">
         <v>33615</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>33615</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>34597.52954417558</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>34597.52954417558</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>34859.85649971863</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>34859.85649971863</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>35599.65953854812</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>35599.65953854812</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>37234.24592009004</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>37234.24592009004</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>39196.1142374789</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>39196.1142374789</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>39016.06359032077</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>39016.06359032077</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>39619.80303882949</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>39619.80303882949</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>40623.30050647158</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>40623.30050647158</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>39064.1530669668</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>39064.1530669668</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>38157.74620146314</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>38157.74620146314</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>39680.6555993247</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>39680.6555993247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>41711.35340461452</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>41711.35340461452</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>41154.33595948227</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>41154.33595948227</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>36805.770962296</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>36805.770962296</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>38144.07146876759</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>38144.07146876759</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>39746.97805289814</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>39746.97805289814</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>41829.41193021948</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>41829.41193021948</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>43202.35509285313</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>43202.35509285313</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>41196.27180641531</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>41196.27180641531</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>40618.51435002814</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>40618.51435002814</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>37282.33539673608</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>37282.33539673608</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>36603.3849184018</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>36603.3849184018</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>39085.5768148565</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>39085.5768148565</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>39205.00281373101</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>39205.00281373101</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>38766.4997186269</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>38766.4997186269</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>39118.62408553743</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>39118.62408553743</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>39902.18626899268</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>39902.18626899268</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>40080.41361845808</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>40080.41361845808</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>39476.90208216095</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>39476.90208216095</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>37266.153629713</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>37266.153629713</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>36568.51435002814</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>36568.51435002814</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>37014.76646032639</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>37014.76646032639</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>38289.25154755206</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>38289.25154755206</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>39062.78559369725</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>39062.78559369725</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>39469.60889138999</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>39469.60889138999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>40337.95441755768</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>40337.95441755768</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>41044.71018570624</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>41044.71018570624</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>41178.49465391108</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>41178.49465391108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>41413.92796848621</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>41413.92796848621</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>39803.72819358469</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>39803.72819358469</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>37370.5374226224</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>37370.5374226224</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>35860.8469330332</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>35860.8469330332</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>36055.25604952167</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>36055.25604952167</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>36794.37535171638</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>36794.37535171638</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>37740.66685424873</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>37740.66685424873</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>37378.51435002814</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>37378.51435002814</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>35819.13899831176</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>35819.13899831176</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>30514.48227349466</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>30514.48227349466</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>29098.23579065841</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>29098.23579065841</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>29618.78728193585</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>29618.78728193585</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>30259.67642093416</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>30259.67642093416</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>30696.12830613393</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>30696.12830613393</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>31551.48283624086</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>31551.48283624086</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>32184.16713562183</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>32184.16713562183</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>32351.91052335397</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>32351.91052335397</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>32885.90883511536</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>32885.90883511536</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>33862.05683736635</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>33862.05683736635</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>34311.72763083849</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>34311.72763083849</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>32339.60326392797</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>32339.60326392797</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>32994.62296004502</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>32994.62296004502</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>34545.33764772088</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>34545.33764772088</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>35131.52785593698</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>35131.52785593698</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>35081.15925717502</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>35081.15925717502</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1961</t>
         </is>
       </c>
     </row>
@@ -724,7 +1712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_2, Fig_5_6, Fig_5_7</t>
+          <t>Fig_5_2, Fig_5_6, Fig_5_7, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -766,138 +1754,151 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S515-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S515-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BLS CES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S515-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S515 — Productive Employment (Lp), narrow classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix E.3 (Labor Statistics), p. 320, row `Lp_total`</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: thousands of workers</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961</t>
+          <t># S515 — Productive Employment (Lp), narrow classification</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Chapter**: 5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix E.3 (Labor Statistics), p. 320, row `Lp_total`</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Units**: thousands of workers</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_partial_1948_1961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Classification Note (important)</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>The book uses two productive labor definitions:</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.453 in 1948. More conservative; excludes some borderline categories.</t>
+          <t>## Classification Note (important)</t>
         </is>
       </c>
     </row>
@@ -909,107 +1910,103 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Both are book-published. They serve different analytical purposes:</t>
+          <t>The book uses two productive labor definitions:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
+          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.453 in 1948. More conservative; excludes some borderline categories.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Both are book-published. They serve different analytical purposes:</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1961 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>## Reference</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>`Lp_total` row values verified directly:</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- 1948 = 29,937 thousand</t>
+          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1961 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- 1961 = 33,615 thousand</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Validator PASS.</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
@@ -1021,41 +2018,77 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>`Lp_total` row values verified directly:</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- 1948 = 29,937 thousand</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>E.3 in the salvaged KB covers 1948-1961 only. The full classification through 1989 would require Tables E.3-continued (later book pages) or BLS CES extension under the same productive boundary definition (non-trivial).</t>
+          <t>- 1961 = 33,615 thousand</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>## Coverage Caveat</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>E.3 in the salvaged KB covers 1948-1961 only. The full classification through 1989 would require Tables E.3-continued (later book pages) or BLS CES extension under the same productive boundary definition (non-trivial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1072,10 +2105,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1100,246 +2133,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lp = employment in productive sectors, classified via the 85 IO sector concordance mapped to 13 NIPA industries. Productive employment includes workers in agriculture (partial), mining, construction, manufacturing, transportation, communications, and utilities. Special decomposition rules apply to agriculture, government enterprises, and FIRE.</t>
+          <t>We must now divide total wages into those of productive and unproductive workers. Given our previous data on the numbers of productive and unproductive workers (Lp, Lu), and on the total wage bill of all workers (W), an estimate of the unit employee compensation of productive workers (ecp) would be sufficient to derive the wage bill of unproductive workers (Wp = ecp · Lp) and also that of unproductive workers (Wu = W - Wp).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.112; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Book period from Table E.3 (Appendix D/E, chunk_30/chunk_31). Extension via BLS Current Employment Statistics (CES) API, using production and nonsupervisory worker counts for goods-producing industries as a proxy for productive employment.</t>
+          <t>Figures 5.10 and 5.11 make quite explicit that the unit wages of productive and unproductive workers change only slightly, whereas their relative employments change drastically. We can therefore unambiguously conclude that the relative decline in productive to total wages Wp/W (= V*/W) is almost entirely due to the relative decline in productive to total employment Lp/L.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_30/full_transcription.md; BLS CES API</t>
+          <t>ST_1994, Ch5, p.113; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.2 shows Lp and Lu trends over time, illustrating the structural shift from productive to unproductive employment. Fig 5.6 relates Lp to total product (TP*) as a productivity measure. Fig 5.7 decomposes total employment into Lp and Lu components.</t>
+          <t>V*/W declines by 34%, while Lp/L declines by 37%.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.2, 5.6, 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.113; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sector_decomposition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agriculture: Lp_agr = (Lp/L)_min × L_agr (uses mining sector productive ratio as proxy). Government enterprises: Lp_ge = (Lp/L)_nongovtot × L_ge. Trade: all employment classified as unproductive (Lu). FIRE: decomposed into finance/insurance, real estate, brokers, and general — each with specific productive/unproductive ratios.</t>
+          <t>Wj = ecj · Lj = estimated wage equivalent of employees and self-employed persons in the jth sector; and W = Sum Wj = total wage and wage equivalent. This extends the coverage of employee compensation to include the wage equivalent of self-employed persons.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.112; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2013) provides alternative employment decomposition using BLS industry codes. His productive employment is higher due to broader classification (Information entirely productive, retail eating/drinking productive). Comparison data in mohun_employment*.csv.</t>
+          <t>Productive labor is the production labor employed in capitalist production sectors: agriculture, mining, construction, transportation and public utilities, manufacturing, and productive services (defined as all services except business services, legal services, and private households, as in Table E.1).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extension_methodology</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BLS CES extension uses production/nonsupervisory workers in goods-producing sectors (mining, construction, manufacturing) plus transportation and utilities. This proxy underestimates Lp by excluding productive workers in mixed sectors but is the most consistent available measure.</t>
+          <t>L_j = total employment in jth sector (from NIPA) = 'persons engaged in production' (PEP) = full-time equivalent employees (FEE) + self-employed persons (SEP); L = ∑L_j = total labor; (Lp/L)_j = ratio of production/total workers in jth production sector (BLS); (Lp)_j = (Lp/L)_j · (L_j) = estimated production worker employment in the jth production sector.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPR T515_DPR.md; EPR T515_EPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BLS CES classification does not perfectly match ST's theoretical framework. The transition from SIC to NAICS industry codes affects time-series consistency. CES production worker definition is occupation-based, while ST's is sector-based.</t>
+          <t>In production sectors, [BLS production and nonsupervisory workers] ≈ production workers.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lp = employment in productive sectors, classified via the 85 IO sector concordance mapped to 13 NIPA industries. Productive employment includes workers in agriculture (partial), mining, construction, manufacturing, transportation, communications, and utilities. Special decomposition rules apply to agriculture, government enterprises, and FIRE.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Productive employment counts workers in productive sectors via 85 IO → 13 NIPA concordance. Special rules for agriculture, government enterprises, trade, and FIRE. Extended via BLS CES production worker data (see DEC-005 in S511/S512).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Book period from Table E.3 (Appendix D/E, chunk_30/chunk_31). Extension via BLS Current Employment Statistics (CES) API, using production and nonsupervisory worker counts for goods-producing industries as a proxy for productive employment.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_30/full_transcription.md; BLS CES API</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 5.2 shows Lp and Lu trends over time, illustrating the structural shift from productive to unproductive employment. Fig 5.6 relates Lp to total product (TP*) as a productivity measure. Fig 5.7 decomposes total employment into Lp and Lu components.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.2, 5.6, 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>sector_decomposition</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agriculture: Lp_agr = (Lp/L)_min × L_agr (uses mining sector productive ratio as proxy). Government enterprises: Lp_ge = (Lp/L)_nongovtot × L_ge. Trade: all employment classified as unproductive (Lu). FIRE: decomposed into finance/insurance, real estate, brokers, and general — each with specific productive/unproductive ratios.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BLS CES production worker ≠ ST's sector-based productive worker</t>
+          <t>Mohun (2013) provides alternative employment decomposition using BLS industry codes. His productive employment is higher due to broader classification (Information entirely productive, retail eating/drinking productive). Comparison data in mohun_employment*.csv.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>extension_methodology</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SIC-to-NAICS transition affects consistency</t>
+          <t>BLS CES extension uses production/nonsupervisory workers in goods-producing sectors (mining, construction, manufacturing) plus transportation and utilities. This proxy underestimates Lp by excluding productive workers in mixed sectors but is the most consistent available measure.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DPR T515_DPR.md; EPR T515_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agriculture and government enterprise use proxy ratios</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Trade classified as entirely unproductive — debatable for some subsectors</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>BLS CES classification does not perfectly match ST's theoretical framework. The transition from SIC to NAICS industry codes affects time-series consistency. CES production worker definition is occupation-based, while ST's is sector-based.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S501</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S511</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S516</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Productive employment counts workers in productive sectors via 85 IO → 13 NIPA concordance. Special rules for agriculture, government enterprises, trade, and FIRE. Extended via BLS CES production worker data (see [internal-decision-record] in S511/S512).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BLS CES production worker ≠ ST's sector-based productive worker</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SIC-to-NAICS transition affects consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Agriculture and government enterprise use proxy ratios</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Trade classified as entirely unproductive — debatable for some subsectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S511</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S516</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>BLS_CES</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Bureau of Labor Statistics. Current Employment Statistics (CES). https://www.bls.gov/ces/</t>
         </is>
@@ -1356,11 +2539,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1452,91 +2635,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S515-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S515-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Appendix E.3 (productive employment Lp, 1948-1961); industry-level employment derived from BLS CES under Appendix C concordance", "shaikh_appendix_ref": "Appendix E.3 Lp series 1948-1961; Table 5.7 (productive labor share Lp/L); coverage limited to 1948-1961 in the salvaged KB digitization", "extension_source": "BLS CES (Current Employment Statistics) industry-level production-worker employment, aggregated through productive/unproductive Appendix C concordance", "extension_url": "https://www.bls.gov/ces/", "conceptual_continuity": "Productive Employment Lp is the count of workers classified as productive under the book's Appendix C concordance. The construct is directly observable in BLS CES at the industry level, subject to the Marxian partition. Conceptual continuity requires updating Appendix C for NAICS industries; otherwise the partition drifts.", "vintage_note": "Book-period KB digitization currently covers 1948-1961 (per Appendix E.3 subset); 1962-1989 book values would require either fuller appendix digitization or BLS CES reconstruction with Appendix C concordance. BLS CES 2003 NAICS overhaul; pre-2003 SIC employment is not directly comparable.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 29937.0, "1961": 33615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[10000, 200000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S515.xlsx
+++ b/extenbooks/S515.xlsx
@@ -505,10 +505,10 @@
         <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>29937</v>
+        <v>32994</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>29937</v>
+        <v>32994</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
@@ -519,10 +519,10 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30013</v>
+        <v>31201</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30013</v>
+        <v>31201</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>30280</v>
+        <v>32226</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30280</v>
+        <v>32226</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -547,10 +547,10 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>31365</v>
+        <v>33123</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>31365</v>
+        <v>33123</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
@@ -561,10 +561,10 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>32566</v>
+        <v>32768</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>32566</v>
+        <v>32768</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
@@ -575,10 +575,10 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>32856</v>
+        <v>33043</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>32856</v>
+        <v>33043</v>
       </c>
       <c r="D8" s="3" t="n">
         <v/>
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>33445</v>
+        <v>31230</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>33445</v>
+        <v>31230</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -603,10 +603,10 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>34125</v>
+        <v>31714</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>34125</v>
+        <v>31714</v>
       </c>
       <c r="D10" s="3" t="n">
         <v/>
@@ -617,10 +617,10 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>33247</v>
+        <v>31864</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>33247</v>
+        <v>31864</v>
       </c>
       <c r="D11" s="3" t="n">
         <v/>
@@ -631,10 +631,10 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>32727</v>
+        <v>31433</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>32727</v>
+        <v>31433</v>
       </c>
       <c r="D12" s="3" t="n">
         <v/>
@@ -645,10 +645,10 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>33896</v>
+        <v>29349</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>33896</v>
+        <v>29349</v>
       </c>
       <c r="D13" s="3" t="n">
         <v/>
@@ -659,10 +659,10 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>35462</v>
+        <v>30020</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>35462</v>
+        <v>30020</v>
       </c>
       <c r="D14" s="3" t="n">
         <v/>
@@ -673,10 +673,10 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>35657</v>
+        <v>30047</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>35657</v>
+        <v>30047</v>
       </c>
       <c r="D15" s="3" t="n">
         <v/>
@@ -687,10 +687,10 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>33615</v>
+        <v>29363</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>33615</v>
+        <v>29363</v>
       </c>
       <c r="D16" s="3" t="n">
         <v/>
@@ -701,13 +701,13 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v/>
+        <v>29937</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>34597.52954417558</v>
+        <v>30221.24825243575</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>34597.52954417558</v>
+        <v>30221.24825243575</v>
       </c>
     </row>
     <row r="18">
@@ -715,13 +715,13 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v/>
+        <v>30013</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>34859.85649971863</v>
+        <v>30450.39316975273</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>34859.85649971863</v>
+        <v>30450.39316975273</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v/>
+        <v>30280</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>35599.65953854812</v>
+        <v>31096.61767158675</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35599.65953854812</v>
+        <v>31096.61767158675</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v/>
+        <v>31365</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>37234.24592009004</v>
+        <v>32524.44334230564</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>37234.24592009004</v>
+        <v>32524.44334230564</v>
       </c>
     </row>
     <row r="21">
@@ -757,13 +757,13 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v/>
+        <v>32566</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>39196.1142374789</v>
+        <v>34238.15268050255</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>39196.1142374789</v>
+        <v>34238.15268050255</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +771,13 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v/>
+        <v>32856</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>39016.06359032077</v>
+        <v>34080.87684672286</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>39016.06359032077</v>
+        <v>34080.87684672286</v>
       </c>
     </row>
     <row r="23">
@@ -785,13 +785,13 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v/>
+        <v>33445</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>39619.80303882949</v>
+        <v>34608.24859821956</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39619.80303882949</v>
+        <v>34608.24859821956</v>
       </c>
     </row>
     <row r="24">
@@ -799,13 +799,13 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v/>
+        <v>34125</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>40623.30050647158</v>
+        <v>35484.81251737395</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>40623.30050647158</v>
+        <v>35484.81251737395</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v/>
+        <v>33247</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39064.1530669668</v>
+        <v>34122.8834301754</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>39064.1530669668</v>
+        <v>34122.8834301754</v>
       </c>
     </row>
     <row r="26">
@@ -827,13 +827,13 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v/>
+        <v>32727</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>38157.74620146314</v>
+        <v>33331.12901126171</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>38157.74620146314</v>
+        <v>33331.12901126171</v>
       </c>
     </row>
     <row r="27">
@@ -841,13 +841,13 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v/>
+        <v>33896</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>39680.6555993247</v>
+        <v>34661.40384837041</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>39680.6555993247</v>
+        <v>34661.40384837041</v>
       </c>
     </row>
     <row r="28">
@@ -855,13 +855,13 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v/>
+        <v>35462</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>41711.35340461452</v>
+        <v>36435.23635340462</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>41711.35340461452</v>
+        <v>36435.23635340462</v>
       </c>
     </row>
     <row r="29">
@@ -869,13 +869,13 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v/>
+        <v>35657</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>41154.33595948227</v>
+        <v>35948.67668535707</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>41154.33595948227</v>
+        <v>35948.67668535707</v>
       </c>
     </row>
     <row r="30">
@@ -883,13 +883,13 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v/>
+        <v>33615</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>36805.770962296</v>
+        <v>32150.16667457676</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>36805.770962296</v>
+        <v>32150.16667457676</v>
       </c>
     </row>
     <row r="31">
@@ -897,13 +897,13 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v/>
+        <v>34677</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>38144.07146876759</v>
+        <v>33319.18401122781</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>38144.07146876759</v>
+        <v>33319.18401122781</v>
       </c>
     </row>
     <row r="32">
@@ -911,13 +911,13 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v/>
+        <v>35798</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>39746.97805289814</v>
+        <v>34719.33709853483</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>39746.97805289814</v>
+        <v>34719.33709853483</v>
       </c>
     </row>
     <row r="33">
@@ -925,13 +925,13 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v/>
+        <v>37610</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>41829.41193021948</v>
+        <v>36538.36152036397</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>41829.41193021948</v>
+        <v>36538.36152036397</v>
       </c>
     </row>
     <row r="34">
@@ -939,13 +939,13 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v/>
+        <v>38598</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>43202.35509285313</v>
+        <v>37737.63952376756</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>43202.35509285313</v>
+        <v>37737.63952376756</v>
       </c>
     </row>
     <row r="35">
@@ -953,13 +953,13 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v/>
+        <v>37863</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>41196.27180641531</v>
+        <v>35985.30801879437</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>41196.27180641531</v>
+        <v>35985.30801879437</v>
       </c>
     </row>
     <row r="36">
@@ -967,13 +967,13 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v/>
+        <v>37738</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>40618.51435002814</v>
+        <v>35480.63176736208</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>40618.51435002814</v>
+        <v>35480.63176736208</v>
       </c>
     </row>
     <row r="37">
@@ -981,13 +981,13 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v/>
+        <v>36203</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>37282.33539673608</v>
+        <v>32566.44992575819</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>37282.33539673608</v>
+        <v>32566.44992575819</v>
       </c>
     </row>
     <row r="38">
@@ -995,13 +995,13 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v/>
+        <v>36088</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>36603.3849184018</v>
+        <v>31973.38067407504</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>36603.3849184018</v>
+        <v>31973.38067407504</v>
       </c>
     </row>
     <row r="39">
@@ -1009,13 +1009,13 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v/>
+        <v>37872</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39085.5768148565</v>
+        <v>34141.59726356185</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>39085.5768148565</v>
+        <v>34141.59726356185</v>
       </c>
     </row>
     <row r="40">
@@ -1023,13 +1023,13 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v/>
+        <v>38229</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>39205.00281373101</v>
+        <v>34245.91693052457</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>39205.00281373101</v>
+        <v>34245.91693052457</v>
       </c>
     </row>
     <row r="41">
@@ -1037,13 +1037,13 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v/>
+        <v>38312</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>38766.4997186269</v>
+        <v>33862.88059610418</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>38766.4997186269</v>
+        <v>33862.88059610418</v>
       </c>
     </row>
     <row r="42">
@@ -1051,13 +1051,13 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v/>
+        <v>39344</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>39118.62408553743</v>
+        <v>34170.46434697711</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>39118.62408553743</v>
+        <v>34170.46434697711</v>
       </c>
     </row>
     <row r="43">
@@ -1065,13 +1065,13 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v/>
+        <v>40538</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>39902.18626899268</v>
+        <v>34854.91284891959</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>39902.18626899268</v>
+        <v>34854.91284891959</v>
       </c>
     </row>
     <row r="44">
@@ -1079,13 +1079,13 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v/>
+        <v>41148</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>40080.41361845808</v>
+        <v>35010.5960160281</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>40080.41361845808</v>
+        <v>35010.5960160281</v>
       </c>
     </row>
     <row r="45">
@@ -1096,10 +1096,10 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>39476.90208216095</v>
+        <v>34483.4233478653</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>39476.90208216095</v>
+        <v>34483.4233478653</v>
       </c>
     </row>
     <row r="46">
@@ -1110,10 +1110,10 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>37266.153629713</v>
+        <v>32552.3150090514</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>37266.153629713</v>
+        <v>32552.3150090514</v>
       </c>
     </row>
     <row r="47">
@@ -1124,10 +1124,10 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>36568.51435002814</v>
+        <v>31942.92092398858</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>36568.51435002814</v>
+        <v>31942.92092398858</v>
       </c>
     </row>
     <row r="48">
@@ -1138,10 +1138,10 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>37014.76646032639</v>
+        <v>32332.72609176153</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>37014.76646032639</v>
+        <v>32332.72609176153</v>
       </c>
     </row>
     <row r="49">
@@ -1152,10 +1152,10 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>38289.25154755206</v>
+        <v>33446.00009492105</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>38289.25154755206</v>
+        <v>33446.00009492105</v>
       </c>
     </row>
     <row r="50">
@@ -1166,10 +1166,10 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>39062.78559369725</v>
+        <v>34121.68893017201</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>39062.78559369725</v>
+        <v>34121.68893017201</v>
       </c>
     </row>
     <row r="51">
@@ -1180,10 +1180,10 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>39469.60889138999</v>
+        <v>34477.05268118055</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>39469.60889138999</v>
+        <v>34477.05268118055</v>
       </c>
     </row>
     <row r="52">
@@ -1194,10 +1194,10 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>40337.95441755768</v>
+        <v>35235.56018333322</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>40337.95441755768</v>
+        <v>35235.56018333322</v>
       </c>
     </row>
     <row r="53">
@@ -1208,10 +1208,10 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>41044.71018570624</v>
+        <v>35852.91760175198</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>41044.71018570624</v>
+        <v>35852.91760175198</v>
       </c>
     </row>
     <row r="54">
@@ -1222,10 +1222,10 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>41178.49465391108</v>
+        <v>35969.77951875029</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>41178.49465391108</v>
+        <v>35969.77951875029</v>
       </c>
     </row>
     <row r="55">
@@ -1236,10 +1236,10 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>41413.92796848621</v>
+        <v>36175.43260266729</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>41413.92796848621</v>
+        <v>36175.43260266729</v>
       </c>
     </row>
     <row r="56">
@@ -1250,10 +1250,10 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>39803.72819358469</v>
+        <v>34768.90884867551</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>39803.72819358469</v>
+        <v>34768.90884867551</v>
       </c>
     </row>
     <row r="57">
@@ -1264,10 +1264,10 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>37370.5374226224</v>
+        <v>32643.49517597685</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>37370.5374226224</v>
+        <v>32643.49517597685</v>
       </c>
     </row>
     <row r="58">
@@ -1278,10 +1278,10 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>35860.8469330332</v>
+        <v>31324.76717223424</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>35860.8469330332</v>
+        <v>31324.76717223424</v>
       </c>
     </row>
     <row r="59">
@@ -1292,10 +1292,10 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>36055.25604952167</v>
+        <v>31494.58525604953</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>36055.25604952167</v>
+        <v>31494.58525604953</v>
       </c>
     </row>
     <row r="60">
@@ -1306,10 +1306,10 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>36794.37535171638</v>
+        <v>32140.21250788184</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>36794.37535171638</v>
+        <v>32140.21250788184</v>
       </c>
     </row>
     <row r="61">
@@ -1320,10 +1320,10 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>37740.66685424873</v>
+        <v>32966.80651022775</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>37740.66685424873</v>
+        <v>32966.80651022775</v>
       </c>
     </row>
     <row r="62">
@@ -1334,10 +1334,10 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>37378.51435002814</v>
+        <v>32650.46309266329</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>37378.51435002814</v>
+        <v>32650.46309266329</v>
       </c>
     </row>
     <row r="63">
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>35819.13899831176</v>
+        <v>31288.33492213085</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>35819.13899831176</v>
+        <v>31288.33492213085</v>
       </c>
     </row>
     <row r="64">
@@ -1362,10 +1362,10 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>30514.48227349466</v>
+        <v>26654.670325647</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>30514.48227349466</v>
+        <v>26654.670325647</v>
       </c>
     </row>
     <row r="65">
@@ -1376,10 +1376,10 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>29098.23579065841</v>
+        <v>25417.56648880271</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>29098.23579065841</v>
+        <v>25417.56648880271</v>
       </c>
     </row>
     <row r="66">
@@ -1390,10 +1390,10 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>29618.78728193585</v>
+        <v>25872.27282342652</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>29618.78728193585</v>
+        <v>25872.27282342652</v>
       </c>
     </row>
     <row r="67">
@@ -1404,10 +1404,10 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>30259.67642093416</v>
+        <v>26432.09515834865</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>30259.67642093416</v>
+        <v>26432.09515834865</v>
       </c>
     </row>
     <row r="68">
@@ -1418,10 +1418,10 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>30696.12830613393</v>
+        <v>26813.33974276397</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>30696.12830613393</v>
+        <v>26813.33974276397</v>
       </c>
     </row>
     <row r="69">
@@ -1432,10 +1432,10 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>31551.48283624086</v>
+        <v>27560.49949488444</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>31551.48283624086</v>
+        <v>27560.49949488444</v>
       </c>
     </row>
     <row r="70">
@@ -1446,10 +1446,10 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>32184.16713562183</v>
+        <v>28113.15482978623</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>32184.16713562183</v>
+        <v>28113.15482978623</v>
       </c>
     </row>
     <row r="71">
@@ -1460,10 +1460,10 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>32351.91052335397</v>
+        <v>28259.68016353541</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>32351.91052335397</v>
+        <v>28259.68016353541</v>
       </c>
     </row>
     <row r="72">
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>32885.90883511536</v>
+        <v>28726.13241485922</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>32885.90883511536</v>
+        <v>28726.13241485922</v>
       </c>
     </row>
     <row r="73">
@@ -1488,10 +1488,10 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>33862.05683736635</v>
+        <v>29578.80633394581</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>33862.05683736635</v>
+        <v>29578.80633394581</v>
       </c>
     </row>
     <row r="74">
@@ -1502,10 +1502,10 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>34311.72763083849</v>
+        <v>29971.59775172722</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>34311.72763083849</v>
+        <v>29971.59775172722</v>
       </c>
     </row>
     <row r="75">
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>32339.60326392797</v>
+        <v>28248.9296635049</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>32339.60326392797</v>
+        <v>28248.9296635049</v>
       </c>
     </row>
     <row r="76">
@@ -1530,10 +1530,10 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>32994.62296004502</v>
+        <v>28821.09516512873</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>32994.62296004502</v>
+        <v>28821.09516512873</v>
       </c>
     </row>
     <row r="77">
@@ -1544,10 +1544,10 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>34545.33764772088</v>
+        <v>30175.65816897302</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>34545.33764772088</v>
+        <v>30175.65816897302</v>
       </c>
     </row>
     <row r="78">
@@ -1558,10 +1558,10 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>35131.52785593698</v>
+        <v>30687.70050375956</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>35131.52785593698</v>
+        <v>30687.70050375956</v>
       </c>
     </row>
     <row r="79">
@@ -1572,10 +1572,10 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>35081.15925717502</v>
+        <v>30643.70308696802</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>35081.15925717502</v>
+        <v>30643.70308696802</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1961</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_partial_1948_1961</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Classification Note (important)</t>
+          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The book uses two productive labor definitions:</t>
+          <t>## Classification Note (important)</t>
         </is>
       </c>
     </row>
@@ -1922,55 +1922,55 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
+          <t>The book uses two productive labor definitions:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.453 in 1948. More conservative; excludes some borderline categories.</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Both are book-published. They serve different analytical purposes:</t>
+          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.453 in 1948. More conservative; excludes some borderline categories.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
+          <t>Both are book-published. They serve different analytical purposes:</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
+          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1961 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1961 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
         </is>
       </c>
     </row>
@@ -2018,23 +2018,19 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>`Lp_total` row values verified directly:</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>- 1948 = 29,937 thousand</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- 1961 = 33,615 thousand</t>
+          <t>`Lp_total` row values verified directly:</t>
         </is>
       </c>
     </row>
@@ -2042,19 +2038,23 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Validator PASS.</t>
+          <t>- 1948 = 29,937 thousand</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- 1961 = 33,615 thousand</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>Validator PASS.</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>E.3 in the salvaged KB covers 1948-1961 only. The full classification through 1989 would require Tables E.3-continued (later book pages) or BLS CES extension under the same productive boundary definition (non-trivial).</t>
+          <t>## Coverage Caveat</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>E.3 in the salvaged KB covers 1948-1961 only. The full classification through 1989 would require Tables E.3-continued (later book pages) or BLS CES extension under the same productive boundary definition (non-trivial).</t>
         </is>
       </c>
     </row>
@@ -2089,6 +2089,18 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -2539,10 +2551,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2746,38 +2758,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1948": 29937.0, "1961": 33615.0}</t>
+          <t>{"1948": 32994.0, "1958": 29349.0, "1967": 32856.0, "1977": 35798.0, "1989": 41148.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[10000, 200000]</t>
+          <t>DIV-013: replaced v1.2 refvals {1948:29937,1961:33615} (a 14-year digitization misalignment of Appendix E.3) with book Table 5.5 'Lp' anchors. Verified vs verbatim book table; panel column-sums to these (identity-consistent).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>[10000, 200000]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2789,24 +2801,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>level_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>tolerance_abs</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S515.xlsx
+++ b/extenbooks/S515.xlsx
@@ -447,13 +447,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +476,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>BLS CES, units=thousands</t>
+          <t>S511 share x CES0000000001 re-anchored @1989, units=thousands</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES CES1000000006+CES2000000006+CES3000000006, unspliced, units=thousands</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>, units=thousands</t>
         </is>
       </c>
     </row>
@@ -497,6 +509,16 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S515-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S515-EXT-CONSTRUCTIBLE</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S515-EXT-OLD-DEPRECATED</t>
         </is>
       </c>
     </row>
@@ -513,6 +535,12 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>15381.9</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -527,6 +555,12 @@
       <c r="D4" s="3" t="n">
         <v/>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>14283.7</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,6 +575,12 @@
       <c r="D5" s="3" t="n">
         <v/>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>15094.2</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -555,6 +595,12 @@
       <c r="D6" s="3" t="n">
         <v/>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>16139</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +615,12 @@
       <c r="D7" s="3" t="n">
         <v/>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>16107.1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,6 +635,12 @@
       <c r="D8" s="3" t="n">
         <v/>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>16696.6</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -597,6 +655,12 @@
       <c r="D9" s="3" t="n">
         <v/>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>15453.6</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -611,6 +675,12 @@
       <c r="D10" s="3" t="n">
         <v/>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>16046</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -625,6 +695,12 @@
       <c r="D11" s="3" t="n">
         <v/>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>16377.6</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -639,6 +715,12 @@
       <c r="D12" s="3" t="n">
         <v/>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>16068.6</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -653,6 +735,12 @@
       <c r="D13" s="3" t="n">
         <v/>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>14733.2</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -667,6 +755,12 @@
       <c r="D14" s="3" t="n">
         <v/>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>15432</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -681,6 +775,12 @@
       <c r="D15" s="3" t="n">
         <v/>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>15321.1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -695,6 +795,12 @@
       <c r="D16" s="3" t="n">
         <v/>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>14749.1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -704,9 +810,15 @@
         <v>29937</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>30221.24825243575</v>
+        <v>29937</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>15180.2</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>30221.24825243575</v>
       </c>
     </row>
@@ -718,9 +830,15 @@
         <v>30013</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>30450.39316975273</v>
+        <v>30013</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>15295.3</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>30450.39316975273</v>
       </c>
     </row>
@@ -732,9 +850,15 @@
         <v>30280</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>31096.61767158675</v>
+        <v>30280</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>15619.9</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>31096.61767158675</v>
       </c>
     </row>
@@ -746,9 +870,15 @@
         <v>31365</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>32524.44334230564</v>
+        <v>31365</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>16337.1</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>32524.44334230564</v>
       </c>
     </row>
@@ -760,9 +890,15 @@
         <v>32566</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>34238.15268050255</v>
+        <v>32566</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>17197.9</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>34238.15268050255</v>
       </c>
     </row>
@@ -774,9 +910,15 @@
         <v>32856</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34080.87684672286</v>
+        <v>32856</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>17118.9</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>34080.87684672286</v>
       </c>
     </row>
@@ -788,9 +930,15 @@
         <v>33445</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>34608.24859821956</v>
+        <v>33445</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>17383.8</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>34608.24859821956</v>
       </c>
     </row>
@@ -802,9 +950,15 @@
         <v>34125</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>35484.81251737395</v>
+        <v>34125</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>17824.1</v>
+      </c>
+      <c r="F24" s="3" t="n">
         <v>35484.81251737395</v>
       </c>
     </row>
@@ -816,9 +970,15 @@
         <v>33247</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34122.8834301754</v>
+        <v>33247</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>17140</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>34122.8834301754</v>
       </c>
     </row>
@@ -830,9 +990,15 @@
         <v>32727</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>33331.12901126171</v>
+        <v>32727</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>16742.3</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>33331.12901126171</v>
       </c>
     </row>
@@ -844,9 +1010,15 @@
         <v>33896</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>34661.40384837041</v>
+        <v>33896</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>17410.5</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>34661.40384837041</v>
       </c>
     </row>
@@ -858,9 +1030,15 @@
         <v>35462</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>36435.23635340462</v>
+        <v>35462</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>18301.5</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>36435.23635340462</v>
       </c>
     </row>
@@ -872,9 +1050,15 @@
         <v>35657</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35948.67668535707</v>
+        <v>35657</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>18057.1</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>35948.67668535707</v>
       </c>
     </row>
@@ -886,9 +1070,15 @@
         <v>33615</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>32150.16667457676</v>
+        <v>33615</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>16149.1</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>32150.16667457676</v>
       </c>
     </row>
@@ -900,9 +1090,15 @@
         <v>34677</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33319.18401122781</v>
+        <v>34677</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>16736.3</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>33319.18401122781</v>
       </c>
     </row>
@@ -914,9 +1110,15 @@
         <v>35798</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>34719.33709853483</v>
+        <v>35798</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>17439.6</v>
+      </c>
+      <c r="F32" s="3" t="n">
         <v>34719.33709853483</v>
       </c>
     </row>
@@ -928,9 +1130,15 @@
         <v>37610</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>36538.36152036397</v>
+        <v>37610</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18353.3</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>36538.36152036397</v>
       </c>
     </row>
@@ -942,9 +1150,15 @@
         <v>38598</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>37737.63952376756</v>
+        <v>38598</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18955.7</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>37737.63952376756</v>
       </c>
     </row>
@@ -956,9 +1170,15 @@
         <v>37863</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>35985.30801879437</v>
+        <v>37863</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>18075.5</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>35985.30801879437</v>
       </c>
     </row>
@@ -970,9 +1190,15 @@
         <v>37738</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>35480.63176736208</v>
+        <v>37738</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17822</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>35480.63176736208</v>
       </c>
     </row>
@@ -984,9 +1210,15 @@
         <v>36203</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>32566.44992575819</v>
+        <v>36203</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>16358.2</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>32566.44992575819</v>
       </c>
     </row>
@@ -998,9 +1230,15 @@
         <v>36088</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>31973.38067407504</v>
+        <v>36088</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>16060.3</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>31973.38067407504</v>
       </c>
     </row>
@@ -1012,9 +1250,15 @@
         <v>37872</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>34141.59726356185</v>
+        <v>37872</v>
       </c>
       <c r="D39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>17149.4</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>34141.59726356185</v>
       </c>
     </row>
@@ -1026,9 +1270,15 @@
         <v>38229</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>34245.91693052457</v>
+        <v>38229</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>17201.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>34245.91693052457</v>
       </c>
     </row>
@@ -1040,9 +1290,15 @@
         <v>38312</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>33862.88059610418</v>
+        <v>38312</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>17009.4</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>33862.88059610418</v>
       </c>
     </row>
@@ -1054,9 +1310,15 @@
         <v>39344</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>34170.46434697711</v>
+        <v>39344</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>17163.9</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>34170.46434697711</v>
       </c>
     </row>
@@ -1068,9 +1330,15 @@
         <v>40538</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>34854.91284891959</v>
+        <v>40538</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>17507.7</v>
+      </c>
+      <c r="F43" s="3" t="n">
         <v>34854.91284891959</v>
       </c>
     </row>
@@ -1082,9 +1350,15 @@
         <v>41148</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>35010.5960160281</v>
+        <v>41148</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>17585.9</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>35010.5960160281</v>
       </c>
     </row>
@@ -1096,9 +1370,15 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>34483.4233478653</v>
+        <v>40844.79162750299</v>
       </c>
       <c r="D45" s="3" t="n">
+        <v>40844.79162750299</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>17321.1</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>34483.4233478653</v>
       </c>
     </row>
@@ -1110,9 +1390,15 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>32552.3150090514</v>
+        <v>39502.9738836874</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>39502.9738836874</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>16351.1</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>32552.3150090514</v>
       </c>
     </row>
@@ -1124,9 +1410,15 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>31942.92092398858</v>
+        <v>39217.04241124708</v>
       </c>
       <c r="D47" s="3" t="n">
+        <v>39217.04241124708</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>16045</v>
+      </c>
+      <c r="F47" s="3" t="n">
         <v>31942.92092398858</v>
       </c>
     </row>
@@ -1138,9 +1430,15 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>32332.72609176153</v>
+        <v>39800.35452140311</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>39800.35452140311</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>16240.8</v>
+      </c>
+      <c r="F48" s="3" t="n">
         <v>32332.72609176153</v>
       </c>
     </row>
@@ -1152,9 +1450,15 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>33446.00009492105</v>
+        <v>41037.77610056663</v>
       </c>
       <c r="D49" s="3" t="n">
+        <v>41037.77610056663</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F49" s="3" t="n">
         <v>33446.00009492105</v>
       </c>
     </row>
@@ -1166,9 +1470,15 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>34121.68893017201</v>
+        <v>41913.29834912381</v>
       </c>
       <c r="D50" s="3" t="n">
+        <v>41913.29834912381</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>17139.4</v>
+      </c>
+      <c r="F50" s="3" t="n">
         <v>34121.68893017201</v>
       </c>
     </row>
@@ -1180,9 +1490,15 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>34477.05268118055</v>
+        <v>42489.14288132476</v>
       </c>
       <c r="D51" s="3" t="n">
+        <v>42489.14288132476</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>17317.9</v>
+      </c>
+      <c r="F51" s="3" t="n">
         <v>34477.05268118055</v>
       </c>
     </row>
@@ -1194,9 +1510,15 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>35235.56018333322</v>
+        <v>43424.91242384192</v>
       </c>
       <c r="D52" s="3" t="n">
+        <v>43424.91242384192</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>17698.9</v>
+      </c>
+      <c r="F52" s="3" t="n">
         <v>35235.56018333322</v>
       </c>
     </row>
@@ -1208,9 +1530,15 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>35852.91760175198</v>
+        <v>44312.30150540785</v>
       </c>
       <c r="D53" s="3" t="n">
+        <v>44312.30150540785</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>18009</v>
+      </c>
+      <c r="F53" s="3" t="n">
         <v>35852.91760175198</v>
       </c>
     </row>
@@ -1222,9 +1550,15 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>35969.77951875029</v>
+        <v>44903.41824363203</v>
       </c>
       <c r="D54" s="3" t="n">
+        <v>44903.41824363203</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>18067.7</v>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>35969.77951875029</v>
       </c>
     </row>
@@ -1236,9 +1570,15 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>36175.43260266729</v>
+        <v>45523.47162113833</v>
       </c>
       <c r="D55" s="3" t="n">
+        <v>45523.47162113833</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>18171</v>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>36175.43260266729</v>
       </c>
     </row>
@@ -1250,9 +1590,15 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>34768.90884867551</v>
+        <v>44715.96069663657</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>44715.96069663657</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>17464.5</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>34768.90884867551</v>
       </c>
     </row>
@@ -1264,9 +1610,15 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>32643.49517597685</v>
+        <v>43247.12154794145</v>
       </c>
       <c r="D57" s="3" t="n">
+        <v>43247.12154794145</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>16396.9</v>
+      </c>
+      <c r="F57" s="3" t="n">
         <v>32643.49517597685</v>
       </c>
     </row>
@@ -1278,9 +1630,15 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>31324.76717223424</v>
+        <v>42382.72464277229</v>
       </c>
       <c r="D58" s="3" t="n">
+        <v>42382.72464277229</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>15734.5</v>
+      </c>
+      <c r="F58" s="3" t="n">
         <v>31324.76717223424</v>
       </c>
     </row>
@@ -1292,9 +1650,15 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>31494.58525604953</v>
+        <v>42701.82559671424</v>
       </c>
       <c r="D59" s="3" t="n">
+        <v>42701.82559671424</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>15819.8</v>
+      </c>
+      <c r="F59" s="3" t="n">
         <v>31494.58525604953</v>
       </c>
     </row>
@@ -1306,9 +1670,15 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>32140.21250788184</v>
+        <v>43468.58931363734</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>43468.58931363734</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>16144.1</v>
+      </c>
+      <c r="F60" s="3" t="n">
         <v>32140.21250788184</v>
       </c>
     </row>
@@ -1320,9 +1690,15 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>32966.80651022775</v>
+        <v>44366.74611684052</v>
       </c>
       <c r="D61" s="3" t="n">
+        <v>44366.74611684052</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>16559.3</v>
+      </c>
+      <c r="F61" s="3" t="n">
         <v>32966.80651022775</v>
       </c>
     </row>
@@ -1334,9 +1710,15 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>32650.46309266329</v>
+        <v>44434.6716583759</v>
       </c>
       <c r="D62" s="3" t="n">
+        <v>44434.6716583759</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>16400.4</v>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>32650.46309266329</v>
       </c>
     </row>
@@ -1348,9 +1730,15 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>31288.33492213085</v>
+        <v>43517.06077299001</v>
       </c>
       <c r="D63" s="3" t="n">
+        <v>43517.06077299001</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>15716.2</v>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>31288.33492213085</v>
       </c>
     </row>
@@ -1362,9 +1750,15 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>26654.670325647</v>
+        <v>39722.54625794037</v>
       </c>
       <c r="D64" s="3" t="n">
+        <v>39722.54625794037</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>13388.7</v>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>26654.670325647</v>
       </c>
     </row>
@@ -1376,9 +1770,15 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>25417.56648880271</v>
+        <v>38783.86681613333</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>38783.86681613333</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>12767.3</v>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>25417.56648880271</v>
       </c>
     </row>
@@ -1390,9 +1790,15 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>25872.27282342652</v>
+        <v>39247.22801060959</v>
       </c>
       <c r="D66" s="3" t="n">
+        <v>39247.22801060959</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>12995.7</v>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>25872.27282342652</v>
       </c>
     </row>
@@ -1404,9 +1810,15 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>26432.09515834865</v>
+        <v>39907.85435945504</v>
       </c>
       <c r="D67" s="3" t="n">
+        <v>39907.85435945504</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>13276.9</v>
+      </c>
+      <c r="F67" s="3" t="n">
         <v>26432.09515834865</v>
       </c>
     </row>
@@ -1418,9 +1830,15 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>26813.33974276397</v>
+        <v>40466.51465626268</v>
       </c>
       <c r="D68" s="3" t="n">
+        <v>40466.51465626268</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>13468.4</v>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>26813.33974276397</v>
       </c>
     </row>
@@ -1432,9 +1850,15 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>27560.49949488444</v>
+        <v>41323.13942948705</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>41323.13942948705</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>13843.7</v>
+      </c>
+      <c r="F69" s="3" t="n">
         <v>27560.49949488444</v>
       </c>
     </row>
@@ -1446,9 +1870,15 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>28113.15482978623</v>
+        <v>42123.55675521419</v>
       </c>
       <c r="D70" s="3" t="n">
+        <v>42123.55675521419</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>14121.3</v>
+      </c>
+      <c r="F70" s="3" t="n">
         <v>28113.15482978623</v>
       </c>
     </row>
@@ -1460,9 +1890,15 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>28259.68016353541</v>
+        <v>42625.96323244725</v>
       </c>
       <c r="D71" s="3" t="n">
+        <v>42625.96323244725</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>14194.9</v>
+      </c>
+      <c r="F71" s="3" t="n">
         <v>28259.68016353541</v>
       </c>
     </row>
@@ -1474,9 +1910,15 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>28726.13241485922</v>
+        <v>43277.65347875428</v>
       </c>
       <c r="D72" s="3" t="n">
+        <v>43277.65347875428</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>14429.2</v>
+      </c>
+      <c r="F72" s="3" t="n">
         <v>28726.13241485922</v>
       </c>
     </row>
@@ -1488,9 +1930,15 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>29578.80633394581</v>
+        <v>44168.84598676208</v>
       </c>
       <c r="D73" s="3" t="n">
+        <v>44168.84598676208</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>14857.5</v>
+      </c>
+      <c r="F73" s="3" t="n">
         <v>29578.80633394581</v>
       </c>
     </row>
@@ -1502,9 +1950,15 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>29971.59775172722</v>
+        <v>44740.34111446716</v>
       </c>
       <c r="D74" s="3" t="n">
+        <v>44740.34111446716</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>15054.8</v>
+      </c>
+      <c r="F74" s="3" t="n">
         <v>29971.59775172722</v>
       </c>
     </row>
@@ -1516,9 +1970,15 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>28248.9296635049</v>
+        <v>42256.04472712302</v>
       </c>
       <c r="D75" s="3" t="n">
+        <v>42256.04472712302</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>14189.5</v>
+      </c>
+      <c r="F75" s="3" t="n">
         <v>28248.9296635049</v>
       </c>
     </row>
@@ -1530,9 +1990,15 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>28821.09516512873</v>
+        <v>43232.74054558259</v>
       </c>
       <c r="D76" s="3" t="n">
+        <v>43232.74054558259</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>14476.9</v>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>28821.09516512873</v>
       </c>
     </row>
@@ -1544,9 +2010,15 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>30175.65816897302</v>
+        <v>45057.12684289972</v>
       </c>
       <c r="D77" s="3" t="n">
+        <v>45057.12684289972</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>15157.3</v>
+      </c>
+      <c r="F77" s="3" t="n">
         <v>30175.65816897302</v>
       </c>
     </row>
@@ -1558,9 +2030,15 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>30687.70050375956</v>
+        <v>45968.67249755292</v>
       </c>
       <c r="D78" s="3" t="n">
+        <v>45968.67249755292</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>15414.5</v>
+      </c>
+      <c r="F78" s="3" t="n">
         <v>30687.70050375956</v>
       </c>
     </row>
@@ -1572,9 +2050,15 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>30643.70308696802</v>
+        <v>46296.3577816349</v>
       </c>
       <c r="D79" s="3" t="n">
+        <v>46296.3577816349</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>15392.4</v>
+      </c>
+      <c r="F79" s="3" t="n">
         <v>30643.70308696802</v>
       </c>
     </row>
@@ -1589,10 +2073,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1785,7 +2269,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLS CES</t>
+          <t>S511 share x CES0000000001 re-anchored @1989</t>
         </is>
       </c>
     </row>
@@ -1797,48 +2281,52 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S515-EXT-CONSTRUCTIBLE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BLS CES CES1000000006+CES2000000006+CES3000000006, unspliced</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>S515-EXT-OLD-DEPRECATED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S515 — Productive Employment (Lp), narrow classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Chapter**: 5</t>
+          <t># S515 — Productive Employment (Lp), narrow classification</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix E.3 (Labor Statistics), p. 320, row `Lp_total`</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Units**: thousands of workers</t>
+          <t>**Chapter**: 5</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2334,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961</t>
+          <t>**Source Table**: Appendix E.3 (Labor Statistics), p. 320, row `Lp_total`</t>
         </is>
       </c>
     </row>
@@ -1854,7 +2342,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Units**: thousands of workers</t>
         </is>
       </c>
     </row>
@@ -1862,19 +2350,23 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Period**: 1948-2024 (book arm 1948-1989; extension 1990-2024)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Content Type**: time_series</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1886,19 +2378,23 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989; V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
+          <t>&gt; **REVIEW_2026-07 item D2 note:** The extension was rebuilt with the book's own share×total construction (candidate (d), user-ratified — see `Handoffs/REVIEW_2026-07/S515_S516_SEAM_REDESIGN.md`). The splice/anchor year is now **1989** for both S515 and S516 (the pre-review code wrongly anchored S515 at 1961, discarding 28 years of genuine book data 1962-1989). `TableE3_LaborStatistics.csv` covers the **full book period 1948-1989** — the earlier "1948-1961 only" coverage claim was false and has been removed throughout.</t>
         </is>
       </c>
     </row>
@@ -1910,7 +2406,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Classification Note (important)</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2418,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The book uses two productive labor definitions:</t>
+          <t>Total productive employment count, summed across sectors with the book's NARROW productive classification (which is more conservative than the BROAD classification used in Table 5.7 / S511).</t>
         </is>
       </c>
     </row>
@@ -1934,35 +2430,31 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
+          <t>## Classification Note (important)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.453 in 1948. More conservative; excludes some borderline categories.</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The book uses two productive labor definitions:</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Both are book-published. They serve different analytical purposes:</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
+          <t>- **Broad** (Table 5.7, S511): Lp/L = 0.57 in 1948. Includes a wider set of activities as productive.</t>
         </is>
       </c>
     </row>
@@ -1970,7 +2462,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
+          <t>- **Narrow** (Table E.3, S515): Lp/L = 0.454 in 1961. More conservative; excludes some borderline categories.</t>
         </is>
       </c>
     </row>
@@ -1982,19 +2474,23 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
+          <t>Both are book-published. They serve different analytical purposes:</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- S511 (broad) drives the exploitation rate decomposition (V*/W).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>- S515 (narrow) is the headcount basis for sector-by-sector labor reconciliation.</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2502,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1961 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
+          <t>The new build keeps BOTH series as first-class, with this DPR documenting the boundary distinction. Cross-checking the two ratios is a useful sensitivity analysis but a difference is not a bug.</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2514,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>&gt; **D2-rebuild correction:** the panel-backed `TableE3` Lp_total gives Lp/L = 0.566 (1948), 0.454 (1961), 0.363 (1989) — see the verified anchors below. Those replace the pre-rebuild degraded-KB values (the old "0.453 in 1948" figure was a mislabeled 1961 value). The D2 extension consumes the **S511 productive share** for both series, so the S515 book arm and the S511 share are reconciled on one productive perimeter rather than treated as divergent narrow/broad head-counts.</t>
         </is>
       </c>
     </row>
@@ -2030,77 +2526,221 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>`Lp_total` row values verified directly:</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>- 1948 = 29,937 thousand</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- 1961 = 33,615 thousand</t>
+          <t>`TableE3_LaborStatistics.csv` is wide-by-year (years 1948-1989 are column headers, sectors are rows). The L01 loader transposes the Lp_total row to a year-indexed series.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Validator PASS.</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>## Reference</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>## Coverage Caveat</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>`Lp_total` row values verified directly against Table 5.5 / Appendix F Table F.1 / `TableE3_LaborStatistics.csv` (all three agree exactly):</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>E.3 in the salvaged KB covers 1948-1961 only. The full classification through 1989 would require Tables E.3-continued (later book pages) or BLS CES extension under the same productive boundary definition (non-trivial).</t>
+          <t>- 1948 = 32,994 thousand (Lp/L = 0.566)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- 1961 = 29,363 thousand (Lp/L = 0.454)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>- 1989 = 41,148 thousand (Lp/L = 0.363)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Validator PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>## Extension (1990-2024) — book share×total construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>The extension follows the book's own method (FULL_TEXT.md L449, verbatim): `(Lp)j = (Lp/L)j·Lj`, `Lp = Σ(Lp)j`, `Lu = L − Lp`. In practice the productive **share** Lp/L is the estimated primitive, and Lp is that share applied to total employment:</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- **S515-EXT** = S511 productive share × book-anchored total employment L. The share is the clean, WP-A-certified **S511-COMBINED** series (BLS CES super-sector Lp/L, additively level-spliced at 1989). Total employment L is BLS CES **total nonfarm all employees including government** (series `CES0000000001`, `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`), multiplicatively re-anchored to the book L (113,511) at 1989. (The pre-review code used total *private* employees CES0500000001, which dropped government and caused the −22% Lu break.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- **S515-COMBINED** = S515-A (book Lp_total, 1948-1989 book values retained) spliced to S515-EXT (1990-2024) at 1989.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Residual concept gap: the total-employment universe excludes self-employed and agriculture; this establishment-vs-household divergence is corrected at the 1989 anchor and is a documented DIV, not a defect. The 2003 SIC→NAICS CES overhaul (DIV-010 family) still applies to the share and the constructible arm below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>**Achieved seam** (extension 1990 vs book 1989): Lp **−0.7%** (book 41,148 → EXT 40,844.8) — continuous, within the 5% guard (previously −15%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sample extension values (`data/final/S515.csv`, `series_id == 'S515-EXT'`, thousands): EXT[1995] = 41,913.3, EXT[2010] = 38,783.9, EXT[2024] = 46,296.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>### Honesty / transparency arms</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Per the S506/S512 two-arm pattern, two additional distinct measures are retained (never consumed as the published Lp):</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **S515-EXT-CONSTRUCTIBLE** — the raw 3-super-sector production-worker count (mining/logging + construction + manufacturing, CES…0006), UNSPLICED. This is the honest BLS-native measure but captures only ~half the book's productive perimeter (super-sector Lp/L ≈ 0.195 vs book 0.363). Sample values: 1990 = 17,321.1; 2024 = 15,392.4 (thousands).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- **S515-EXT-OLD-DEPRECATED** — the frozen pre-review arm (raw super-sector count level-spliced at 1961). DEPRECATED, retained for transparency only; it discarded book data 1962-1989 — do not consume. Sample values: 1990 = 34,483.4; 2024 = 30,643.7 (thousands).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -2551,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2689,7 +3329,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>share_times_total@1989 (Lp = (Lp/L)·L per book method FULL_TEXT L449: S511 productive share × book-anchored total-employment L incl. government; anchored at the true 1989 overlap; book A retained for all book years 1948-1989)</t>
         </is>
       </c>
     </row>
@@ -2737,71 +3377,71 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
+          <t>["S511 (productive share Lp/L, S511-COMBINED)", "Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001, total nonfarm incl. govt)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor = 113511)"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>anchor_year</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{"1948": 32994.0, "1958": 29349.0, "1967": 32856.0, "1977": 35798.0, "1989": 41148.0}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>v1.3_patch</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIV-013: replaced v1.2 refvals {1948:29937,1961:33615} (a 14-year digitization misalignment of Appendix E.3) with book Table 5.5 'Lp' anchors. Verified vs verbatim book table; panel column-sums to these (identity-consistent).</t>
+          <t>{"1948": 32994.0, "1958": 29349.0, "1967": 32856.0, "1977": 35798.0, "1989": 41148.0}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[10000, 200000]</t>
+          <t>DIV-013: replaced v1.2 refvals {1948:29937,1961:33615} (a 14-year digitization misalignment of Appendix E.3) with book Table 5.5 'Lp' anchors. Verified vs verbatim book table; panel column-sums to these (identity-consistent).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>[10000, 200000]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2813,34 +3453,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>level_series</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>extension_year_range</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>[1948, 2024]</t>
         </is>

--- a/extenbooks/S515.xlsx
+++ b/extenbooks/S515.xlsx
@@ -2630,7 +2630,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **S515-EXT** = S511 productive share × book-anchored total employment L. The share is the clean, WP-A-certified **S511-COMBINED** series (BLS CES super-sector Lp/L, additively level-spliced at 1989). Total employment L is BLS CES **total nonfarm all employees including government** (series `CES0000000001`, `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`), multiplicatively re-anchored to the book L (113,511) at 1989. (The pre-review code used total *private* employees CES0500000001, which dropped government and caused the −22% Lu break.)</t>
+          <t>- **S515-EXT** = S511 productive share × book-anchored total employment L. The share is the clean, WP-A-certified **S511-COMBINED** series (BLS CES super-sector Lp/L, additively level-spliced at 1989). Total employment L is BLS CES **total nonfarm all employees including government** (series `CES0000000001`, `data/raw/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`), multiplicatively re-anchored to the book L (113,511) at 1989. (The pre-review code used total *private* employees CES0500000001, which dropped government and caused the −22% Lu break.)</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["S511 (productive share Lp/L, S511-COMBINED)", "Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001, total nonfarm incl. govt)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor = 113511)"]</t>
+          <t>["S511 (productive share Lp/L, S511-COMBINED)", "data/raw/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001, total nonfarm incl. govt)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor = 113511)"]</t>
         </is>
       </c>
     </row>
